--- a/csv/MMI-Data.xlsx
+++ b/csv/MMI-Data.xlsx
@@ -1,20 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19440" windowHeight="7635" tabRatio="761"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635" tabRatio="761"/>
   </bookViews>
   <sheets>
     <sheet name="STUDENT DATA 26-27" sheetId="1" r:id="rId1"/>
+    <sheet name="Toddlers" sheetId="6" r:id="rId2"/>
+    <sheet name="Play Group" sheetId="2" r:id="rId3"/>
+    <sheet name="Nursery" sheetId="3" r:id="rId4"/>
+    <sheet name="Pre-Nursery" sheetId="4" r:id="rId5"/>
+    <sheet name="Kindergarden" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STUDENT DATA 26-27'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STUDENT DATA 26-27'!$A$1:$I$175</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="789">
   <si>
     <t>REGISTRATION NO</t>
   </si>
@@ -2386,16 +2397,28 @@
   </si>
   <si>
     <t>manpreetkourbali@gmail.com</t>
+  </si>
+  <si>
+    <t>bloomers</t>
+  </si>
+  <si>
+    <t>azalea</t>
+  </si>
+  <si>
+    <t>buttercup</t>
+  </si>
+  <si>
+    <t>camellia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2902,16 +2925,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I175"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J175"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.42578125" style="18" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" style="21" customWidth="1"/>
@@ -2920,11 +2943,11 @@
     <col min="5" max="5" width="13.42578125" style="5" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" style="5" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="10" customFormat="1">
+    <row r="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>6</v>
       </c>
@@ -2952,8 +2975,11 @@
       <c r="I1" s="10" t="s">
         <v>642</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="10" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>7</v>
       </c>
@@ -2981,8 +3007,11 @@
       <c r="I2" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
@@ -3010,8 +3039,11 @@
       <c r="I3" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>634</v>
       </c>
@@ -3039,8 +3071,11 @@
       <c r="I4" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>9</v>
       </c>
@@ -3068,8 +3103,11 @@
       <c r="I5" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
@@ -3097,8 +3135,11 @@
       <c r="I6" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>11</v>
       </c>
@@ -3126,8 +3167,11 @@
       <c r="I7" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>12</v>
       </c>
@@ -3155,8 +3199,11 @@
       <c r="I8" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>13</v>
       </c>
@@ -3184,8 +3231,11 @@
       <c r="I9" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>14</v>
       </c>
@@ -3213,8 +3263,11 @@
       <c r="I10" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>15</v>
       </c>
@@ -3242,8 +3295,11 @@
       <c r="I11" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>596</v>
       </c>
@@ -3271,8 +3327,11 @@
       <c r="I12" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>16</v>
       </c>
@@ -3300,8 +3359,11 @@
       <c r="I13" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>17</v>
       </c>
@@ -3329,8 +3391,11 @@
       <c r="I14" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>18</v>
       </c>
@@ -3358,8 +3423,11 @@
       <c r="I15" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="21" customHeight="1">
+      <c r="J15" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>317</v>
       </c>
@@ -3387,8 +3455,11 @@
       <c r="I16" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>19</v>
       </c>
@@ -3416,8 +3487,11 @@
       <c r="I17" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
@@ -3445,8 +3519,11 @@
       <c r="I18" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
@@ -3474,8 +3551,11 @@
       <c r="I19" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J19" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>22</v>
       </c>
@@ -3503,8 +3583,11 @@
       <c r="I20" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>23</v>
       </c>
@@ -3532,8 +3615,11 @@
       <c r="I21" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>24</v>
       </c>
@@ -3561,8 +3647,11 @@
       <c r="I22" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>25</v>
       </c>
@@ -3590,8 +3679,11 @@
       <c r="I23" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>26</v>
       </c>
@@ -3619,8 +3711,11 @@
       <c r="I24" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>27</v>
       </c>
@@ -3648,8 +3743,11 @@
       <c r="I25" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>28</v>
       </c>
@@ -3677,8 +3775,11 @@
       <c r="I26" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>29</v>
       </c>
@@ -3706,8 +3807,11 @@
       <c r="I27" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>30</v>
       </c>
@@ -3735,8 +3839,11 @@
       <c r="I28" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>31</v>
       </c>
@@ -3764,8 +3871,11 @@
       <c r="I29" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>32</v>
       </c>
@@ -3793,8 +3903,11 @@
       <c r="I30" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>33</v>
       </c>
@@ -3822,8 +3935,11 @@
       <c r="I31" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>34</v>
       </c>
@@ -3851,8 +3967,11 @@
       <c r="I32" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="J32" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>35</v>
       </c>
@@ -3880,8 +3999,11 @@
       <c r="I33" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J33" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>36</v>
       </c>
@@ -3909,8 +4031,11 @@
       <c r="I34" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="J34" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
         <v>37</v>
       </c>
@@ -3938,8 +4063,11 @@
       <c r="I35" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="J35" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>38</v>
       </c>
@@ -3967,8 +4095,11 @@
       <c r="I36" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="J36" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>39</v>
       </c>
@@ -3996,8 +4127,11 @@
       <c r="I37" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="J37" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
         <v>172</v>
       </c>
@@ -4025,8 +4159,11 @@
       <c r="I38" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="J38" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>40</v>
       </c>
@@ -4054,8 +4191,11 @@
       <c r="I39" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="J39" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>41</v>
       </c>
@@ -4083,8 +4223,11 @@
       <c r="I40" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="J40" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>127</v>
       </c>
@@ -4109,8 +4252,11 @@
       <c r="I41" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="J41" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>42</v>
       </c>
@@ -4138,8 +4284,11 @@
       <c r="I42" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="22.5" customHeight="1">
+      <c r="J42" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>43</v>
       </c>
@@ -4167,8 +4316,11 @@
       <c r="I43" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="J43" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>44</v>
       </c>
@@ -4196,8 +4348,11 @@
       <c r="I44" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="19.5" customHeight="1">
+      <c r="J44" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>165</v>
       </c>
@@ -4225,8 +4380,11 @@
       <c r="I45" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="J45" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
         <v>166</v>
       </c>
@@ -4250,8 +4408,11 @@
       <c r="I46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="J46" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>167</v>
       </c>
@@ -4279,8 +4440,11 @@
       <c r="I47" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="J47" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
         <v>168</v>
       </c>
@@ -4308,8 +4472,11 @@
       <c r="I48" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="J48" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>169</v>
       </c>
@@ -4337,8 +4504,11 @@
       <c r="I49" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="J49" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
         <v>170</v>
       </c>
@@ -4366,8 +4536,11 @@
       <c r="I50" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="J50" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>171</v>
       </c>
@@ -4395,8 +4568,11 @@
       <c r="I51" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="J51" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
         <v>366</v>
       </c>
@@ -4424,8 +4600,11 @@
       <c r="I52" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="J52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>174</v>
       </c>
@@ -4453,8 +4632,11 @@
       <c r="I53" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="J53" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
         <v>175</v>
       </c>
@@ -4482,8 +4664,11 @@
       <c r="I54" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="J54" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>176</v>
       </c>
@@ -4511,8 +4696,11 @@
       <c r="I55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="J55" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
         <v>177</v>
       </c>
@@ -4540,8 +4728,11 @@
       <c r="I56" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="J56" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>190</v>
       </c>
@@ -4563,8 +4754,11 @@
       <c r="I57" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="58" spans="1:9">
+      <c r="J57" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
         <v>191</v>
       </c>
@@ -4592,8 +4786,11 @@
       <c r="I58" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="59" spans="1:9">
+      <c r="J58" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
         <v>229</v>
       </c>
@@ -4621,8 +4818,11 @@
       <c r="I59" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="60" spans="1:9">
+      <c r="J59" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
         <v>195</v>
       </c>
@@ -4650,8 +4850,11 @@
       <c r="I60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="J60" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>209</v>
       </c>
@@ -4679,8 +4882,11 @@
       <c r="I61" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="J61" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>404</v>
       </c>
@@ -4702,8 +4908,11 @@
       <c r="I62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9">
+      <c r="J62" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>210</v>
       </c>
@@ -4731,8 +4940,11 @@
       <c r="I63" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="64" spans="1:9">
+      <c r="J63" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>260</v>
       </c>
@@ -4760,8 +4972,11 @@
       <c r="I64" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="J64" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>384</v>
       </c>
@@ -4786,8 +5001,11 @@
       <c r="I65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="J65" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>306</v>
       </c>
@@ -4815,8 +5033,11 @@
       <c r="I66" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="67" spans="1:9">
+      <c r="J66" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>307</v>
       </c>
@@ -4844,8 +5065,11 @@
       <c r="I67" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="68" spans="1:9">
+      <c r="J67" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>310</v>
       </c>
@@ -4873,8 +5097,11 @@
       <c r="I68" t="s">
         <v>700</v>
       </c>
-    </row>
-    <row r="69" spans="1:9">
+      <c r="J68" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>318</v>
       </c>
@@ -4902,8 +5129,11 @@
       <c r="I69" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="70" spans="1:9">
+      <c r="J69" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
         <v>321</v>
       </c>
@@ -4931,8 +5161,11 @@
       <c r="I70" t="s">
         <v>702</v>
       </c>
-    </row>
-    <row r="71" spans="1:9">
+      <c r="J70" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>324</v>
       </c>
@@ -4960,8 +5193,11 @@
       <c r="I71" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="72" spans="1:9">
+      <c r="J71" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
         <v>327</v>
       </c>
@@ -4989,8 +5225,11 @@
       <c r="I72" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="73" spans="1:9">
+      <c r="J72" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
         <v>330</v>
       </c>
@@ -5018,8 +5257,11 @@
       <c r="I73" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="74" spans="1:9">
+      <c r="J73" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>641</v>
       </c>
@@ -5047,8 +5289,11 @@
       <c r="I74" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="75" spans="1:9">
+      <c r="J74" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
         <v>336</v>
       </c>
@@ -5076,8 +5321,11 @@
       <c r="I75" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="76" spans="1:9">
+      <c r="J75" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
         <v>333</v>
       </c>
@@ -5102,8 +5350,11 @@
       <c r="I76" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="77" spans="1:9">
+      <c r="J76" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
         <v>339</v>
       </c>
@@ -5131,8 +5382,11 @@
       <c r="I77" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="78" spans="1:9">
+      <c r="J77" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
         <v>342</v>
       </c>
@@ -5160,8 +5414,11 @@
       <c r="I78" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="79" spans="1:9">
+      <c r="J78" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
         <v>344</v>
       </c>
@@ -5189,8 +5446,11 @@
       <c r="I79" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="80" spans="1:9">
+      <c r="J79" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
         <v>345</v>
       </c>
@@ -5218,8 +5478,11 @@
       <c r="I80" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="81" spans="1:9">
+      <c r="J80" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
         <v>350</v>
       </c>
@@ -5247,8 +5510,11 @@
       <c r="I81" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="82" spans="1:9">
+      <c r="J81" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
         <v>353</v>
       </c>
@@ -5276,8 +5542,11 @@
       <c r="I82" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="83" spans="1:9">
+      <c r="J82" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="18" t="s">
         <v>356</v>
       </c>
@@ -5305,8 +5574,11 @@
       <c r="I83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9">
+      <c r="J83" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="20" t="s">
         <v>359</v>
       </c>
@@ -5334,8 +5606,11 @@
       <c r="I84" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="85" spans="1:9">
+      <c r="J84" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="20" t="s">
         <v>361</v>
       </c>
@@ -5363,8 +5638,11 @@
       <c r="I85" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="86" spans="1:9">
+      <c r="J85" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
         <v>362</v>
       </c>
@@ -5392,8 +5670,11 @@
       <c r="I86" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="J86" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>365</v>
       </c>
@@ -5418,8 +5699,11 @@
       <c r="I87" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="88" spans="1:9">
+      <c r="J87" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="20" t="s">
         <v>367</v>
       </c>
@@ -5447,8 +5731,11 @@
       <c r="I88" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="89" spans="1:9">
+      <c r="J88" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
         <v>368</v>
       </c>
@@ -5476,8 +5763,11 @@
       <c r="I89" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="90" spans="1:9">
+      <c r="J89" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
         <v>378</v>
       </c>
@@ -5505,8 +5795,11 @@
       <c r="I90" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="91" spans="1:9">
+      <c r="J90" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="18" t="s">
         <v>369</v>
       </c>
@@ -5534,8 +5827,11 @@
       <c r="I91" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="92" spans="1:9">
+      <c r="J91" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="18" t="s">
         <v>581</v>
       </c>
@@ -5563,8 +5859,11 @@
       <c r="I92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:9">
+      <c r="J92" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
         <v>574</v>
       </c>
@@ -5592,8 +5891,11 @@
       <c r="I93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:9">
+      <c r="J93" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="s">
         <v>370</v>
       </c>
@@ -5621,8 +5923,11 @@
       <c r="I94" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="95" spans="1:9">
+      <c r="J94" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
         <v>374</v>
       </c>
@@ -5650,8 +5955,11 @@
       <c r="I95" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="96" spans="1:9">
+      <c r="J95" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
         <v>376</v>
       </c>
@@ -5679,8 +5987,11 @@
       <c r="I96" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="97" spans="1:9">
+      <c r="J96" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
         <v>589</v>
       </c>
@@ -5708,8 +6019,11 @@
       <c r="I97" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="98" spans="1:9">
+      <c r="J97" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
         <v>529</v>
       </c>
@@ -5737,8 +6051,11 @@
       <c r="I98" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="99" spans="1:9">
+      <c r="J98" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="18" t="s">
         <v>379</v>
       </c>
@@ -5763,8 +6080,11 @@
       <c r="I99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:9">
+      <c r="J99" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
         <v>380</v>
       </c>
@@ -5792,8 +6112,11 @@
       <c r="I100" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="101" spans="1:9">
+      <c r="J100" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="18" t="s">
         <v>381</v>
       </c>
@@ -5821,8 +6144,11 @@
       <c r="I101" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="102" spans="1:9">
+      <c r="J101" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="18" t="s">
         <v>382</v>
       </c>
@@ -5850,8 +6176,11 @@
       <c r="I102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:9">
+      <c r="J102" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="18" t="s">
         <v>383</v>
       </c>
@@ -5879,8 +6208,11 @@
       <c r="I103" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="104" spans="1:9">
+      <c r="J103" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
         <v>393</v>
       </c>
@@ -5908,8 +6240,11 @@
       <c r="I104" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="105" spans="1:9">
+      <c r="J104" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
         <v>385</v>
       </c>
@@ -5937,8 +6272,11 @@
       <c r="I105" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="106" spans="1:9">
+      <c r="J105" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
         <v>388</v>
       </c>
@@ -5966,8 +6304,11 @@
       <c r="I106" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="107" spans="1:9">
+      <c r="J106" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
         <v>391</v>
       </c>
@@ -5995,8 +6336,11 @@
       <c r="I107" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="108" spans="1:9">
+      <c r="J107" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
         <v>420</v>
       </c>
@@ -6024,8 +6368,11 @@
       <c r="I108" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="109" spans="1:9">
+      <c r="J108" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
         <v>423</v>
       </c>
@@ -6050,8 +6397,11 @@
       <c r="I109" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="110" spans="1:9">
+      <c r="J109" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
         <v>424</v>
       </c>
@@ -6079,8 +6429,11 @@
       <c r="I110" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="111" spans="1:9">
+      <c r="J110" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
         <v>427</v>
       </c>
@@ -6108,8 +6461,11 @@
       <c r="I111" t="s">
         <v>734</v>
       </c>
-    </row>
-    <row r="112" spans="1:9">
+      <c r="J111" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
         <v>428</v>
       </c>
@@ -6137,8 +6493,11 @@
       <c r="I112" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="113" spans="1:9">
+      <c r="J112" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
         <v>481</v>
       </c>
@@ -6166,8 +6525,11 @@
       <c r="I113" t="s">
         <v>736</v>
       </c>
-    </row>
-    <row r="114" spans="1:9">
+      <c r="J113" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="s">
         <v>434</v>
       </c>
@@ -6195,8 +6557,11 @@
       <c r="I114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:9">
+      <c r="J114" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
         <v>437</v>
       </c>
@@ -6224,8 +6589,11 @@
       <c r="I115" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="116" spans="1:9">
+      <c r="J115" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="s">
         <v>440</v>
       </c>
@@ -6253,8 +6621,11 @@
       <c r="I116" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="117" spans="1:9">
+      <c r="J116" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
         <v>441</v>
       </c>
@@ -6282,8 +6653,11 @@
       <c r="I117" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="118" spans="1:9">
+      <c r="J117" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
         <v>442</v>
       </c>
@@ -6311,8 +6685,11 @@
       <c r="I118" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="119" spans="1:9">
+      <c r="J118" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
         <v>445</v>
       </c>
@@ -6340,8 +6717,11 @@
       <c r="I119" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="120" spans="1:9">
+      <c r="J119" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="s">
         <v>447</v>
       </c>
@@ -6369,8 +6749,11 @@
       <c r="I120" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="121" spans="1:9">
+      <c r="J120" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
         <v>448</v>
       </c>
@@ -6398,8 +6781,11 @@
       <c r="I121" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="122" spans="1:9">
+      <c r="J121" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="s">
         <v>451</v>
       </c>
@@ -6427,8 +6813,11 @@
       <c r="I122" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="123" spans="1:9">
+      <c r="J122" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
         <v>452</v>
       </c>
@@ -6456,8 +6845,11 @@
       <c r="I123" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="124" spans="1:9">
+      <c r="J123" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
         <v>457</v>
       </c>
@@ -6485,8 +6877,11 @@
       <c r="I124" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="125" spans="1:9">
+      <c r="J124" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
         <v>459</v>
       </c>
@@ -6514,8 +6909,11 @@
       <c r="I125" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="126" spans="1:9">
+      <c r="J125" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
         <v>461</v>
       </c>
@@ -6543,8 +6941,11 @@
       <c r="I126" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="127" spans="1:9">
+      <c r="J126" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
         <v>464</v>
       </c>
@@ -6572,8 +6973,11 @@
       <c r="I127" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="128" spans="1:9">
+      <c r="J127" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
         <v>467</v>
       </c>
@@ -6601,8 +7005,11 @@
       <c r="I128" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="129" spans="1:9">
+      <c r="J128" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
         <v>468</v>
       </c>
@@ -6630,8 +7037,11 @@
       <c r="I129" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="130" spans="1:9">
+      <c r="J129" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
         <v>471</v>
       </c>
@@ -6659,8 +7069,11 @@
       <c r="I130" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="131" spans="1:9">
+      <c r="J130" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="18" t="s">
         <v>473</v>
       </c>
@@ -6688,8 +7101,11 @@
       <c r="I131" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="132" spans="1:9">
+      <c r="J131" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="18" t="s">
         <v>476</v>
       </c>
@@ -6714,8 +7130,11 @@
       <c r="I132" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="133" spans="1:9">
+      <c r="J132" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>557</v>
       </c>
@@ -6741,8 +7160,11 @@
       <c r="I133" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="134" spans="1:9">
+      <c r="J133" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="18" t="s">
         <v>487</v>
       </c>
@@ -6767,8 +7189,11 @@
       <c r="I134" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="135" spans="1:9">
+      <c r="J134" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
         <v>484</v>
       </c>
@@ -6796,8 +7221,11 @@
       <c r="I135" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="136" spans="1:9">
+      <c r="J135" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="s">
         <v>491</v>
       </c>
@@ -6825,8 +7253,11 @@
       <c r="I136" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="137" spans="1:9">
+      <c r="J136" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
         <v>611</v>
       </c>
@@ -6854,8 +7285,11 @@
       <c r="I137" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="138" spans="1:9">
+      <c r="J137" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="25" t="s">
         <v>496</v>
       </c>
@@ -6883,8 +7317,11 @@
       <c r="I138" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="139" spans="1:9">
+      <c r="J138" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>499</v>
       </c>
@@ -6913,7 +7350,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
         <v>503</v>
       </c>
@@ -6935,8 +7372,11 @@
       <c r="I140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:9">
+      <c r="J140" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="18" t="s">
         <v>504</v>
       </c>
@@ -6964,8 +7404,11 @@
       <c r="I141" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="142" spans="1:9">
+      <c r="J141" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>457</v>
       </c>
@@ -6993,8 +7436,11 @@
       <c r="I142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:9">
+      <c r="J142" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>509</v>
       </c>
@@ -7022,8 +7468,11 @@
       <c r="I143" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="144" spans="1:9">
+      <c r="J143" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="18" t="s">
         <v>511</v>
       </c>
@@ -7051,8 +7500,11 @@
       <c r="I144" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="145" spans="1:9">
+      <c r="J144" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="18" t="s">
         <v>512</v>
       </c>
@@ -7080,8 +7532,11 @@
       <c r="I145" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="146" spans="1:9">
+      <c r="J145" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="18" t="s">
         <v>515</v>
       </c>
@@ -7106,8 +7561,11 @@
       <c r="I146" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="147" spans="1:9">
+      <c r="J146" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="18" t="s">
         <v>520</v>
       </c>
@@ -7135,8 +7593,11 @@
       <c r="I147" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="148" spans="1:9">
+      <c r="J147" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="18" t="s">
         <v>523</v>
       </c>
@@ -7164,8 +7625,11 @@
       <c r="I148" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="149" spans="1:9">
+      <c r="J148" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="18" t="s">
         <v>524</v>
       </c>
@@ -7193,8 +7657,11 @@
       <c r="I149" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="150" spans="1:9">
+      <c r="J149" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
         <v>558</v>
       </c>
@@ -7222,8 +7689,11 @@
       <c r="I150" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="151" spans="1:9">
+      <c r="J150" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
         <v>532</v>
       </c>
@@ -7251,8 +7721,11 @@
       <c r="I151" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="152" spans="1:9">
+      <c r="J151" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="18" t="s">
         <v>535</v>
       </c>
@@ -7280,8 +7753,11 @@
       <c r="I152" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="153" spans="1:9">
+      <c r="J152" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>538</v>
       </c>
@@ -7309,8 +7785,11 @@
       <c r="I153" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="154" spans="1:9">
+      <c r="J153" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
         <v>540</v>
       </c>
@@ -7338,8 +7817,11 @@
       <c r="I154" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="155" spans="1:9">
+      <c r="J154" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="18" t="s">
         <v>543</v>
       </c>
@@ -7367,8 +7849,11 @@
       <c r="I155" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="156" spans="1:9">
+      <c r="J155" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
         <v>546</v>
       </c>
@@ -7396,8 +7881,11 @@
       <c r="I156" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="157" spans="1:9">
+      <c r="J156" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
         <v>552</v>
       </c>
@@ -7425,8 +7913,11 @@
       <c r="I157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:9">
+      <c r="J157" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
         <v>559</v>
       </c>
@@ -7454,8 +7945,11 @@
       <c r="I158" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="159" spans="1:9">
+      <c r="J158" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
         <v>562</v>
       </c>
@@ -7483,8 +7977,11 @@
       <c r="I159" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="160" spans="1:9">
+      <c r="J159" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
         <v>565</v>
       </c>
@@ -7512,8 +8009,11 @@
       <c r="I160" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="161" spans="1:9">
+      <c r="J160" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
         <v>568</v>
       </c>
@@ -7541,8 +8041,11 @@
       <c r="I161" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="162" spans="1:9">
+      <c r="J161" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
         <v>571</v>
       </c>
@@ -7570,8 +8073,11 @@
       <c r="I162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:9">
+      <c r="J162" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
         <v>575</v>
       </c>
@@ -7599,8 +8105,11 @@
       <c r="I163" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="164" spans="1:9">
+      <c r="J163" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="18" t="s">
         <v>578</v>
       </c>
@@ -7625,8 +8134,11 @@
       <c r="I164" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="165" spans="1:9">
+      <c r="J164" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
         <v>582</v>
       </c>
@@ -7654,8 +8166,11 @@
       <c r="I165" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="166" spans="1:9">
+      <c r="J165" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
         <v>583</v>
       </c>
@@ -7683,8 +8198,11 @@
       <c r="I166" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="167" spans="1:9">
+      <c r="J166" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="18" t="s">
         <v>587</v>
       </c>
@@ -7712,8 +8230,11 @@
       <c r="I167" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="168" spans="1:9">
+      <c r="J167" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="18" t="s">
         <v>592</v>
       </c>
@@ -7735,8 +8256,11 @@
       <c r="I168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:9">
+      <c r="J168" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="18" t="s">
         <v>594</v>
       </c>
@@ -7764,8 +8288,11 @@
       <c r="I169" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="170" spans="1:9">
+      <c r="J169" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="18" t="s">
         <v>599</v>
       </c>
@@ -7790,8 +8317,11 @@
       <c r="I170" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="171" spans="1:9">
+      <c r="J170" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
         <v>616</v>
       </c>
@@ -7819,8 +8349,11 @@
       <c r="I171" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="172" spans="1:9">
+      <c r="J171" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
         <v>628</v>
       </c>
@@ -7848,8 +8381,11 @@
       <c r="I172" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="173" spans="1:9">
+      <c r="J172" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
         <v>623</v>
       </c>
@@ -7877,8 +8413,11 @@
       <c r="I173" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="174" spans="1:9">
+      <c r="J173" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
         <v>624</v>
       </c>
@@ -7906,8 +8445,11 @@
       <c r="I174" t="e">
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="175" spans="1:9">
+      <c r="J174" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="18" t="s">
         <v>638</v>
       </c>
@@ -7935,10 +8477,7444 @@
       <c r="I175" t="e">
         <v>#N/A</v>
       </c>
+      <c r="J175" t="s">
+        <v>787</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I175"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" s="21">
+        <v>514</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="E2" s="5">
+        <v>9596771111</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="G2" s="9">
+        <v>9873957363</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2" s="21">
+        <v>496</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" s="5">
+        <v>9419245264</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G2" s="1">
+        <v>9419284546</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B3" s="21">
+        <v>494</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="21">
+        <v>504</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="5">
+        <v>9796645804</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" s="7">
+        <v>7889415321</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I4" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>452</v>
+      </c>
+      <c r="B5" s="21">
+        <v>507</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="5">
+        <v>8825042625</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="G5" s="7">
+        <v>9797514777</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="B6" s="21">
+        <v>503</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="5">
+        <v>9796085940</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="G6" s="7">
+        <v>7780995676</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="B7" s="21">
+        <v>500</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E7" s="5">
+        <v>8899995471</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="G7" s="7">
+        <v>9711349755</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I7" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="21">
+        <v>508</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="E8" s="5">
+        <v>979719999</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="21">
+        <v>511</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="E9" s="22">
+        <v>9872150677</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="G9" s="9">
+        <v>9796444683</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="21">
+        <v>525</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>492</v>
+      </c>
+      <c r="E10" s="22">
+        <v>7006323727</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="G10" s="9">
+        <v>9906072020</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I10" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>503</v>
+      </c>
+      <c r="B11" s="21">
+        <v>521</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="G11" s="9">
+        <v>7006287502</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" s="21">
+        <v>526</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="E12" s="5">
+        <v>9205011111</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G12" s="1">
+        <v>8082951360</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9419197792</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="G13" s="1">
+        <v>9419141554</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I13" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="B14" s="21">
+        <v>517</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9596661555</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9419109913</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I14" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>523</v>
+      </c>
+      <c r="B15" s="21">
+        <v>527</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8800030300</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="G15" s="1">
+        <v>9796220727</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I15" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="B16" s="21">
+        <v>520</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="E16" s="5">
+        <v>7006282974</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G16" s="1">
+        <v>9682153546</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I16" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>532</v>
+      </c>
+      <c r="B17" s="21">
+        <v>529</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="E17" s="5">
+        <v>7308200001</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="G17" s="1">
+        <v>7837619608</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I17" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="B18" s="21">
+        <v>538</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="E18" s="5">
+        <v>7006271237</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="G18" s="1">
+        <v>7889841042</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I18" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="B19" s="21">
+        <v>528</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="E19" s="5">
+        <v>8826461469</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="G19" s="1">
+        <v>7340732713</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I19" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>565</v>
+      </c>
+      <c r="B20" s="21">
+        <v>531</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="E20" s="5">
+        <v>9103697447</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="G20" s="1">
+        <v>7780858505</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I20" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>568</v>
+      </c>
+      <c r="B21" s="21">
+        <v>532</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="E21" s="5">
+        <v>9419188300</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="G21" s="1">
+        <v>9419109384</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I21" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>571</v>
+      </c>
+      <c r="B22" s="21">
+        <v>533</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="E22" s="5">
+        <v>7006334203</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="G22" s="1">
+        <v>9797461185</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="B23" s="21">
+        <v>545</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="E23" s="5">
+        <v>9419193888</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9796423311</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I23" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>587</v>
+      </c>
+      <c r="B24" s="21">
+        <v>536</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="E24" s="5">
+        <v>61425292836</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6005981374</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="I24" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="B25" s="21">
+        <v>544</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="E25" s="5">
+        <v>9858020106</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="G25" s="1">
+        <v>9149925543</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="I25" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>599</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="E26" s="5">
+        <v>7889019537</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="G26" s="1">
+        <v>9149505250</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="I26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="B27" s="21">
+        <v>542</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="E27" s="5">
+        <v>9419782409</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="G27" s="1">
+        <v>9018535553</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I27" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="B28" s="21">
+        <v>546</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="E28" s="5">
+        <v>9469122222</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9796085832</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="E2" s="5">
+        <v>9906197777</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="5">
+        <v>8803844444</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G4" s="2">
+        <v>9070594444</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G5" s="2">
+        <v>7889415321</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="21">
+        <v>413</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E20" s="5">
+        <v>8795947000</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="G20" s="2">
+        <v>8492817349</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E21" s="5">
+        <v>889977777</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" s="5">
+        <v>9622222232</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G22" s="2">
+        <v>8717003888</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" s="21">
+        <v>415</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="5">
+        <v>9622933197</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="1">
+        <v>9797550123</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="21">
+        <v>420</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" s="5">
+        <v>9419184575</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G24" s="1">
+        <v>9419900999</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B25" s="21">
+        <v>416</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="5">
+        <v>7006430892</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G25" s="1">
+        <v>9419393861</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="21">
+        <v>419</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="5">
+        <v>9796209885</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G26" s="1">
+        <v>7006798707</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="21">
+        <v>418</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="5">
+        <v>9419100611</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="1">
+        <v>8825097053</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="21">
+        <v>421</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9419786061</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="21">
+        <v>423</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E29" s="5">
+        <v>8713994444</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G29" s="1">
+        <v>8899989000</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" s="21">
+        <v>422</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="5">
+        <v>9086333333</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G30" s="1">
+        <v>9555072113</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="21">
+        <v>425</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" s="5">
+        <v>9910301228</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G31" s="1">
+        <v>9796659282</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="21">
+        <v>427</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E32" s="5">
+        <v>9176040407</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="1">
+        <v>7780915147</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" s="21">
+        <v>428</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E33" s="5">
+        <v>9086778999</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G33" s="1">
+        <v>9086684999</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B34" s="21">
+        <v>429</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E34" s="5">
+        <v>7022630313</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G34" s="1">
+        <v>9419384373</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="B35" s="21">
+        <v>430</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E35" s="5">
+        <v>9622684746</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G35" s="1">
+        <v>6005181318</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B36" s="21">
+        <v>435</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E36" s="5">
+        <v>9650110984</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G36" s="1">
+        <v>9650110984</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B37" s="21">
+        <v>436</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E37" s="5">
+        <v>9796388203</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G37" s="1">
+        <v>9356333334</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B38" s="21">
+        <v>438</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E38" s="5">
+        <v>9906113333</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G38" s="1">
+        <v>8716013333</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B39" s="21">
+        <v>447</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E39" s="5">
+        <v>7838041979</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G39" s="1">
+        <v>8800170018</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B40" s="21">
+        <v>444</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E40" s="5">
+        <v>9769272171</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="B41" s="21">
+        <v>456</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E41" s="5">
+        <v>9419779999</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G41" s="1">
+        <v>9419399999</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B42" s="21">
+        <v>467</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E42" s="5">
+        <v>9541389457</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="G42" s="1">
+        <v>9419144928</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B43" s="21">
+        <v>480</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E43" s="5">
+        <v>8816087110</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G43" s="1">
+        <v>8950600777</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B44" s="21">
+        <v>399</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="B45" s="21">
+        <v>464</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E45" s="5">
+        <v>7006082991</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="G45" s="1">
+        <v>7889744643</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B46" s="21">
+        <v>468</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="E46" s="5">
+        <v>7889624767</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G46" s="1">
+        <v>7006783291</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="B47" s="21">
+        <v>475</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E47" s="5">
+        <v>7006127379</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="G47" s="1">
+        <v>7006127256</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I47" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="B48" s="21">
+        <v>485</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E48" s="5">
+        <v>9419148821</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G48" s="1">
+        <v>8171143322</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="B49" s="21">
+        <v>505</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="E49" s="5">
+        <v>7889881995</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G49" s="1">
+        <v>6005713016</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="B50" s="21">
+        <v>541</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="E50" s="5">
+        <v>8803600001</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="G50" s="1">
+        <v>7006146110</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="B51" s="21">
+        <v>534</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="E51" s="5">
+        <v>9419227612</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G51" s="1">
+        <v>7006277491</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>592</v>
+      </c>
+      <c r="B52" s="21">
+        <v>540</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="G52" s="1">
+        <v>7889901163</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="B2" s="21">
+        <v>539</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="E2" s="21">
+        <v>8899118111</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="G2" s="21">
+        <v>9882643286</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E4" s="5">
+        <v>9920796005</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7889855140</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="21">
+        <v>434</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E5" s="5">
+        <v>9018877777</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="21">
+        <v>433</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="5">
+        <v>9419125225</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="1">
+        <v>9419102006</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I6" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="21">
+        <v>432</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" s="5">
+        <v>9469100000</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" s="1">
+        <v>8899967788</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B8" s="21">
+        <v>450</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="5">
+        <v>9419797684</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G8" s="1">
+        <v>9622409966</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B9" s="21">
+        <v>451</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E9" s="5">
+        <v>9419797684</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9622409966</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="B10" s="21">
+        <v>481</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E10" s="5">
+        <v>7860000097</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G10" s="1">
+        <v>7006605314</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B11" s="21">
+        <v>439</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E11" s="5">
+        <v>7006897283</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G11" s="1">
+        <v>9796663322</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B12" s="21">
+        <v>440</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G12" s="1">
+        <v>9596831440</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="B13" s="21">
+        <v>482</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="5">
+        <v>9070355555</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G13" s="1">
+        <v>9070377777</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="B14" s="21">
+        <v>489</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9419276660</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G14" s="1">
+        <v>7889623936</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" s="21">
+        <v>442</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E15" s="5">
+        <v>9906027777</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G15" s="1">
+        <v>9899954766</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="B16" s="21">
+        <v>446</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8717012356</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7298116494</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="21">
+        <v>449</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E17" s="5">
+        <v>9796076880</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G17" s="1">
+        <v>9596814898</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" s="21">
+        <v>454</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E18" s="5">
+        <v>9055511022</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G18" s="1">
+        <v>8717060024</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B19" s="21">
+        <v>483</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B20" s="21">
+        <v>445</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" s="5">
+        <v>9906087001</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G20" s="1">
+        <v>7006980044</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B21" s="21">
+        <v>458</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E21" s="5">
+        <v>9419183575</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G21" s="1">
+        <v>9419183575</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B22" s="21">
+        <v>459</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E22" s="5">
+        <v>9419183575</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G22" s="1">
+        <v>9419183575</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" s="21">
+        <v>461</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" s="5">
+        <v>7889885434</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G23" s="1">
+        <v>7006656099</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="B24" s="21">
+        <v>477</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E24" s="5">
+        <v>9419145317</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="G24" s="1">
+        <v>9796291011</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="B25" s="21">
+        <v>460</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E25" s="5">
+        <v>7006886659</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G25" s="1">
+        <v>7006886659</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B26" s="21">
+        <v>462</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G26" s="1">
+        <v>8899100567</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B27" s="21">
+        <v>463</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E27" s="5">
+        <v>9205000095</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G27" s="1">
+        <v>8769602044</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="21">
+        <v>471</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="E28" s="5">
+        <v>9796430333</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9858503033</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I28" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="B29" s="21">
+        <v>478</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="E29" s="5">
+        <v>9596624092</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G29" s="1">
+        <v>705159997</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I29" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="21">
+        <v>472</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="5">
+        <v>9419231724</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="G30" s="1">
+        <v>9419278309</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I30" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B31" s="21">
+        <v>473</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="5">
+        <v>9596927723</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G31" s="1">
+        <v>7889972738</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I31" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B32" s="21">
+        <v>486</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E32" s="5">
+        <v>9797513131</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G32" s="1">
+        <v>8825026334</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="B33" s="21">
+        <v>487</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E33" s="5">
+        <v>9419155000</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G33" s="1">
+        <v>9797205500</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I33" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="B34" s="21">
+        <v>488</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E34" s="5">
+        <v>9560073579</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G34" s="1">
+        <v>8716025456</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I34" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="B35" s="21">
+        <v>490</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="E35" s="5">
+        <v>9419147562</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="G35" s="1">
+        <v>7889945981</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I35" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B36" s="21">
+        <v>492</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E36" s="5">
+        <v>7006171300</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6006068133</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="B37" s="21">
+        <v>491</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="E37" s="5">
+        <v>9419106378</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="G37" s="1">
+        <v>9419106378</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I37" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="B38" s="21">
+        <v>493</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="5">
+        <v>8082031234</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="G38" s="1">
+        <v>8492937360</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I38" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="B39" s="21">
+        <v>495</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="E39" s="5">
+        <v>8717000025</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G39" s="1">
+        <v>9858778089</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I39" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="B40" s="21">
+        <v>498</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E40" s="5">
+        <v>9419210008</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="G40" s="1">
+        <v>8825097540</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I40" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="B41" s="21">
+        <v>497</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E41" s="5">
+        <v>9541638748</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="G41" s="1">
+        <v>7780865533</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I41" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="B42" s="21">
+        <v>502</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="5">
+        <v>9906143229</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="G42" s="1">
+        <v>7006736563</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="I42" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="B43" s="21">
+        <v>499</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E43" s="5">
+        <v>9205000000</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="1">
+        <v>7889667293</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I43" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B44" s="21">
+        <v>501</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="E44" s="5">
+        <v>9419213737</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="G44" s="1">
+        <v>9419240383</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I44" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="B45" s="21">
+        <v>506</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="E45" s="5">
+        <v>9797536121</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="G45" s="1">
+        <v>7006718805</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I45" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="B46" s="21">
+        <v>510</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="E46" s="5">
+        <v>9810196580</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="G46" s="7">
+        <v>9899766011</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="I46" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="B47" s="21">
+        <v>509</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22" t="s">
+        <v>556</v>
+      </c>
+      <c r="G47" s="9">
+        <v>9103037514</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I47" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="B48" s="21"/>
+      <c r="C48" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="E48" s="22">
+        <v>8803233858</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="G48" s="9">
+        <v>7780929070</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="I48" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="B49" s="21">
+        <v>512</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="E49" s="22">
+        <v>9116939143</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="G49" s="9">
+        <v>9672515585</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="I49" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="B50" s="21">
+        <v>513</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E50" s="22">
+        <v>9599143158</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="G50" s="9">
+        <v>7006286345</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="I50" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="18" t="s">
+        <v>504</v>
+      </c>
+      <c r="B51" s="21">
+        <v>519</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="E51" s="5">
+        <v>9018051010</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="G51" s="1">
+        <v>6006332344</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I51" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="B52" s="21">
+        <v>523</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E52" s="5">
+        <v>9149730189</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="G52" s="1">
+        <v>7780806497</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="B53" s="21">
+        <v>515</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E53" s="5">
+        <v>9650924327</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="G53" s="1">
+        <v>9086296322</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="B54" s="21">
+        <v>516</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="E54" s="5">
+        <v>9796667777</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="G54" s="1">
+        <v>8713005555</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="B55" s="21">
+        <v>518</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="E55" s="5">
+        <v>9797836027</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="G55" s="1">
+        <v>9086025776</v>
+      </c>
+      <c r="H55" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="I55" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="B56" s="21">
+        <v>530</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="E56" s="5">
+        <v>7006701144</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="G56" s="1">
+        <v>9070090659</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>538</v>
+      </c>
+      <c r="B57" s="21">
+        <v>524</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="E57" s="5">
+        <v>9797929292</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G57" s="1">
+        <v>9797029292</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>540</v>
+      </c>
+      <c r="B58" s="21">
+        <v>522</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="E58" s="5">
+        <v>9419122956</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="G58" s="1">
+        <v>6005849327</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="B59" s="21">
+        <v>543</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="E59" s="5">
+        <v>9906089889</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9796068774</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>552</v>
+      </c>
+      <c r="B60" s="21">
+        <v>537</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="E60" s="5">
+        <v>9086077727</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="G60" s="1">
+        <v>9467707336</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>578</v>
+      </c>
+      <c r="B61" s="21"/>
+      <c r="C61" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="E61" s="5">
+        <v>9622022266</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G61" s="1">
+        <v>8492000500</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I61" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>583</v>
+      </c>
+      <c r="B62" s="21">
+        <v>535</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="E62" s="5">
+        <v>9419227612</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G62" s="1">
+        <v>7006277491</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B63" s="21">
+        <v>474</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="E63" s="5">
+        <v>9419155351</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="G63" s="1">
+        <v>9419151942</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="I63" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="B64" s="21">
+        <v>453</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="E64" s="5">
+        <v>9419105000</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="G64" s="1">
+        <v>9103005000</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I64" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="B65" s="21">
+        <v>465</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="E65" s="5">
+        <v>7889632857</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="G65" s="1">
+        <v>9419104969</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="I65" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I109"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="E3" s="5">
+        <v>9906197777</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>634</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I6" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I7" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I8" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I9" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I10" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I11" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="B12" s="21">
+        <v>539</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="E12" s="21">
+        <v>8899118111</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="G12" s="21">
+        <v>9882643286</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I13" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9810020062</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I14" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" s="2">
+        <v>7780915147</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I15" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="5">
+        <v>7006992994</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G16" s="2">
+        <v>9682586120</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I16" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G17" s="2">
+        <v>7006238116</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I17" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G18" s="2">
+        <v>9070107003</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I18" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G19" s="2">
+        <v>9086082545</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I19" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="2">
+        <v>8082911234</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I20" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="E21" s="5">
+        <v>8803844444</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G21" s="2">
+        <v>9070594444</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="G22" s="2">
+        <v>7889415321</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I23" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I24" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I25" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I27" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I28" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I43" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I44" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="21">
+        <v>413</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E45" s="5">
+        <v>8795947000</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="G45" s="2">
+        <v>8492817349</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D46" s="15"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E47" s="5">
+        <v>889977777</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="5">
+        <v>9815131601</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="I48" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="E49" s="5">
+        <v>9622222232</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G49" s="2">
+        <v>8717003888</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" s="5">
+        <v>9920796005</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G50" s="2">
+        <v>7889855140</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="21">
+        <v>414</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" s="5">
+        <v>9988660264</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="G51" s="1">
+        <v>96409980011</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="I51" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B52" s="21">
+        <v>415</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="E52" s="5">
+        <v>9622933197</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="G52" s="1">
+        <v>9797550123</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="21">
+        <v>420</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="5">
+        <v>9419184575</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G53" s="1">
+        <v>9419900999</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B54" s="21">
+        <v>416</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" s="5">
+        <v>7006430892</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G54" s="1">
+        <v>9419393861</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B55" s="21">
+        <v>419</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" s="5">
+        <v>9796209885</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G55" s="1">
+        <v>7006798707</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" s="21">
+        <v>418</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="5">
+        <v>9419100611</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G56" s="1">
+        <v>8825097053</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B57" s="21">
+        <v>421</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G57" s="1">
+        <v>9419786061</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" s="21">
+        <v>423</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E58" s="5">
+        <v>8713994444</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="G58" s="1">
+        <v>8899989000</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="21">
+        <v>422</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E59" s="5">
+        <v>9086333333</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="G59" s="1">
+        <v>9555072113</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" s="21">
+        <v>425</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="E60" s="5">
+        <v>9910301228</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G60" s="1">
+        <v>9796659282</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B61" s="21">
+        <v>427</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="E61" s="5">
+        <v>9176040407</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G61" s="1">
+        <v>7780915147</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="B62" s="21">
+        <v>332</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="E62" s="5">
+        <v>7006507007</v>
+      </c>
+      <c r="F62" s="5"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B63" s="21">
+        <v>428</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E63" s="5">
+        <v>9086778999</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="G63" s="1">
+        <v>9086684999</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I63" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" s="21">
+        <v>429</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E64" s="5">
+        <v>7022630313</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" s="1">
+        <v>9419384373</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I64" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B65" s="21">
+        <v>434</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E65" s="5">
+        <v>9018877777</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="B66" s="21">
+        <v>430</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="E66" s="5">
+        <v>9622684746</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G66" s="1">
+        <v>6005181318</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I66" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B67" s="21">
+        <v>433</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E67" s="5">
+        <v>9419125225</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="G67" s="1">
+        <v>9419102006</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I67" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B68" s="21">
+        <v>432</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="E68" s="5">
+        <v>9469100000</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G68" s="1">
+        <v>8899967788</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I68" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="B69" s="21">
+        <v>435</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E69" s="5">
+        <v>9650110984</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G69" s="1">
+        <v>9650110984</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" s="21">
+        <v>436</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E70" s="5">
+        <v>9796388203</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" s="1">
+        <v>9356333334</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I70" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B71" s="21">
+        <v>438</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="E71" s="5">
+        <v>9906113333</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G71" s="1">
+        <v>8716013333</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I71" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="B72" s="21">
+        <v>450</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E72" s="5">
+        <v>9419797684</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G72" s="1">
+        <v>9622409966</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B73" s="21">
+        <v>451</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="E73" s="5">
+        <v>9419797684</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G73" s="1">
+        <v>9622409966</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I73" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="18" t="s">
+        <v>641</v>
+      </c>
+      <c r="B74" s="21">
+        <v>481</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E74" s="5">
+        <v>7860000097</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="G74" s="1">
+        <v>7006605314</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I74" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B75" s="21">
+        <v>439</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="E75" s="5">
+        <v>7006897283</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="G75" s="1">
+        <v>9796663322</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I75" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B76" s="21">
+        <v>440</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G76" s="1">
+        <v>9596831440</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="B77" s="21">
+        <v>482</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E77" s="5">
+        <v>9070355555</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G77" s="1">
+        <v>9070377777</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I77" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="B78" s="21">
+        <v>489</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="E78" s="5">
+        <v>9419276660</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G78" s="1">
+        <v>7889623936</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="B79" s="21">
+        <v>441</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E79" s="5">
+        <v>9906587051</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="G79" s="1">
+        <v>9906672006</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="I79" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B80" s="21">
+        <v>442</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E80" s="5">
+        <v>9906027777</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G80" s="1">
+        <v>9899954766</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="B81" s="21">
+        <v>446</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="E81" s="5">
+        <v>8717012356</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G81" s="1">
+        <v>7298116494</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B82" s="21">
+        <v>449</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E82" s="5">
+        <v>9796076880</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G82" s="1">
+        <v>9596814898</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B83" s="21">
+        <v>454</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E83" s="5">
+        <v>9055511022</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="G83" s="1">
+        <v>8717060024</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B84" s="21">
+        <v>447</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E84" s="5">
+        <v>7838041979</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G84" s="1">
+        <v>8800170018</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I84" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="B85" s="21">
+        <v>483</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I85" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="B86" s="21">
+        <v>445</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E86" s="5">
+        <v>9906087001</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="G86" s="1">
+        <v>7006980044</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B87" s="21">
+        <v>444</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E87" s="5">
+        <v>9769272171</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I87" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="B88" s="21">
+        <v>458</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E88" s="5">
+        <v>9419183575</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G88" s="1">
+        <v>9419183575</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I88" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B89" s="21">
+        <v>459</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E89" s="5">
+        <v>9419183575</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G89" s="1">
+        <v>9419183575</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B90" s="21">
+        <v>461</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="E90" s="5">
+        <v>7889885434</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="G90" s="1">
+        <v>7006656099</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I90" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="B91" s="21">
+        <v>477</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="E91" s="5">
+        <v>9419145317</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="G91" s="1">
+        <v>9796291011</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="18" t="s">
+        <v>581</v>
+      </c>
+      <c r="B92" s="21">
+        <v>460</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E92" s="5">
+        <v>7006886659</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="G92" s="1">
+        <v>7006886659</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="B93" s="21">
+        <v>456</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E93" s="5">
+        <v>9419779999</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="G93" s="1">
+        <v>9419399999</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="B94" s="21">
+        <v>455</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E94" s="5">
+        <v>7006055007</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G94" s="1">
+        <v>9906060897</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="I94" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B95" s="21">
+        <v>467</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="E95" s="5">
+        <v>9541389457</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="G95" s="1">
+        <v>9419144928</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I95" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B96" s="21">
+        <v>480</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="E96" s="5">
+        <v>8816087110</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="G96" s="1">
+        <v>8950600777</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I96" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="18" t="s">
+        <v>589</v>
+      </c>
+      <c r="B97" s="21">
+        <v>327</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="E97" s="5">
+        <v>7006222041</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="G97" s="1">
+        <v>7889453528</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="I97" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="18" t="s">
+        <v>529</v>
+      </c>
+      <c r="B98" s="21">
+        <v>399</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I98" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B99" s="21">
+        <v>462</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G99" s="1">
+        <v>8899100567</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B100" s="21">
+        <v>463</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E100" s="5">
+        <v>9205000095</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G100" s="1">
+        <v>8769602044</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="B101" s="21">
+        <v>464</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E101" s="5">
+        <v>7006082991</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="G101" s="1">
+        <v>7889744643</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I101" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B102" s="21">
+        <v>468</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="E102" s="5">
+        <v>7889624767</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G102" s="1">
+        <v>7006783291</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B103" s="21">
+        <v>471</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="E103" s="5">
+        <v>9796430333</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="G103" s="1">
+        <v>9858503033</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I103" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="B104" s="21">
+        <v>478</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="E104" s="5">
+        <v>9596624092</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G104" s="1">
+        <v>705159997</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I104" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B105" s="21">
+        <v>472</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E105" s="5">
+        <v>9419231724</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="G105" s="1">
+        <v>9419278309</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I105" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B106" s="21">
+        <v>473</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="E106" s="5">
+        <v>9596927723</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G106" s="1">
+        <v>7889972738</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="I106" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="B107" s="21">
+        <v>475</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E107" s="5">
+        <v>7006127379</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="G107" s="1">
+        <v>7006127256</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I107" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="B108" s="21">
+        <v>486</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="E108" s="5">
+        <v>9797513131</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="G108" s="1">
+        <v>8825026334</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I108" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="B109" s="21">
+        <v>484</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="E109" s="5">
+        <v>8716000041</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="I109" t="s">
+        <v>732</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>